--- a/model_info/gpt_domain.xlsx
+++ b/model_info/gpt_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="25.3" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="26.400000000000002" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.06986370919713651</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.028703089142484234</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>0.36918175090963323</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.7722395614865794</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.4634660664110746</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.4297738391517053</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         <v>0.771408411398117</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.14444444444444446</v>
+        <v>0.49905149051490516</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.92955711169917</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.8491502727720733</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
     </row>
     <row r="12">
@@ -981,7 +981,7 @@
         <v>0.32589175953011573</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.1283068783068783</v>
+        <v>0.5029289493575207</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.08450426027607655</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.45036453356892464</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.18207718207718207</v>
+        <v>0.5126072184895715</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.9018724962079787</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.30518518518518517</v>
+        <v>0.5162289562289563</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.5750675939670482</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.3327380952380953</v>
+        <v>0.5189331501831502</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.7984476718786792</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.1326388888888889</v>
+        <v>0.4774305555555555</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.446228015923701</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.0068936877076411955</v>
+        <v>0.29756449091264414</v>
       </c>
     </row>
     <row r="20">
@@ -1373,7 +1373,7 @@
         <v>0.10794704599197937</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.0880952380952381</v>
+        <v>0.42946428571428574</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/gpt_domain.xlsx
+++ b/model_info/gpt_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="25.3" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.06986370919713651</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.028703089142484234</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>0.36918175090963323</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.7722395614865794</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.4634660664110746</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.4297738391517053</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         <v>0.771408411398117</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.49905149051490516</v>
+        <v>0.12330623306233063</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.92955711169917</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.8491502727720733</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
     </row>
     <row r="12">
@@ -981,7 +981,7 @@
         <v>0.32589175953011573</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.5029289493575207</v>
+        <v>0.1125958319835871</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.08450426027607655</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.45036453356892464</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.5126072184895715</v>
+        <v>0.15351605547683977</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.9018724962079787</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.5162289562289563</v>
+        <v>0.22195286195286196</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.5750675939670482</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.5189331501831502</v>
+        <v>0.23462301587301587</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.7984476718786792</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.4774305555555555</v>
+        <v>0.10905864197530864</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.446228015923701</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.29756449091264414</v>
+        <v>0.004055110416259527</v>
       </c>
     </row>
     <row r="20">
@@ -1373,7 +1373,7 @@
         <v>0.10794704599197937</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.42946428571428574</v>
+        <v>0.06790674603174604</v>
       </c>
     </row>
   </sheetData>
